--- a/BTech/Python-Competencies  mapping with QPs -BTech.xlsx
+++ b/BTech/Python-Competencies  mapping with QPs -BTech.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSDU\BTech\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSDU_GIT\BTech\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6768"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10512"/>
   </bookViews>
   <sheets>
     <sheet name="Specifications" sheetId="2" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Sr.  No.</t>
   </si>
@@ -120,26 +120,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1. Develop Python programs that accept user inputs, process numeric and textual data, and generate correct outputs for defined computational requirements.
-2. Implement conditional and iterative logic to control program execution for validation, classification, calculation, and repeated processing tasks.
-3. Manipulate strings, lists, tuples, sets, and dictionaries to store, retrieve, transform, and process application data.
-4. Create modular Python solutions using user-defined functions, arguments, lambda expressions, and relevant modules for reusable program components.
-5. Diagnose syntax, runtime, logical, and input-handling errors; create test cases; and refine Python programs for correct execution.
-6. Develop basic desktop applications using Tkinter and object-oriented design, incorporating APIs or introductory concurrency features where required in mini projects.
-7. Use Vibe Coding (AI-assisted development) to generate, refine, test, and debug Python code effectively
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-CO1: Develop Python programs to solve structured computational problems using appropriate variables, data types, expressions, and input-output operations.
-CO2: Construct Python solutions that use decision-making and looping constructs to address defined logical and repetitive problem situations.
-CO3: Create and evaluate python programs that organise and process data using collections and string-manipulation operations.
-CO4: Design modular Python programs by applying functions, functional expressions, and modules to improve solution structure and reusability.
-CO5: Test, debug, and improve Python programs through systematic identification of errors and validation of expected program behaviour.
-CO6: Develop simple Python-based desktop applications by integrating graphical interfaces, object-oriented programming, external data access, and introductory concurrency concepts.
-</t>
-  </si>
-  <si>
     <t>Lab equipments , infrastructure and Software</t>
   </si>
   <si>
@@ -151,12 +131,40 @@
   <si>
     <t xml:space="preserve">Software Development with Python </t>
   </si>
+  <si>
+    <t>2. Implement structured program logic for validation, classification, calculation, and repeated processing using conditional and iterative constructs.</t>
+  </si>
+  <si>
+    <t>3. Construct data-processing solutions by organising, transforming, and retrieving textual and structured data using appropriate Python collection types.</t>
+  </si>
+  <si>
+    <t>4. Develop reusable Python application components using functions, functional expressions, modules, and object-oriented constructs for defined software requirements.</t>
+  </si>
+  <si>
+    <t>5. Create and refine basic desktop applications by integrating graphical interfaces, external data access, introductory concurrency, testing, debugging, and AI-assisted development practices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Develop Python-based computational solutions for defined requirements by selecting suitable data representations, program logic, and input-output operations.
+2. Implement structured program logic for validation, classification, calculation, and repeated processing using conditional and iterative constructs.
+3. Construct data-processing solutions by organising, transforming, and retrieving textual and structured data using appropriate Python collection types.
+4. Develop reusable Python application components using functions, functional expressions, modules, and object-oriented constructs for defined software requirements.
+5. Create and refine basic desktop applications by integrating graphical interfaces, external data access, introductory concurrency, testing, debugging, and AI-assisted development practices.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO1: Develop Python programs for structured computational problems using variables, data types, expressions, type conversion, and input-output operations.
+CO2: Construct Python solutions using conditional statements, iterative constructs, and loop-control statements for defined logical and repetitive-processing tasks.
+CO3: Create Python programs that manipulate strings, lists, tuples, sets, and dictionaries to store, retrieve, transform, and process application data.
+CO4: Design modular Python programs using user-defined functions, recursion, lambda expressions, built-in functions, modules, classes, and objects.
+CO5: Develop, test, debug, and refine Tkinter-based desktop applications integrating event handling, external APIs, introductory concurrency, and validated AI-assisted code.
+</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -201,11 +209,16 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -297,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -331,11 +344,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -592,10 +611,10 @@
         <v>11</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>12</v>
@@ -636,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>24</v>
@@ -663,7 +682,7 @@
         <v>16</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L2" s="9" t="s">
         <v>19</v>
@@ -680,14 +699,14 @@
       <c r="P2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="Q2" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="13" t="s">
-        <v>28</v>
+      <c r="R2" s="16" t="s">
+        <v>36</v>
       </c>
-      <c r="S2" s="13" t="s">
-        <v>29</v>
+      <c r="S2" s="16" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="13.2">
@@ -708,8 +727,9 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
-    </row>
-    <row r="4" spans="1:19" ht="13.2">
+      <c r="R3" s="14"/>
+    </row>
+    <row r="4" spans="1:19" ht="55.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -727,6 +747,9 @@
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
+      <c r="R4" s="15" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="5" spans="1:19" ht="13.2">
       <c r="A5" s="2"/>
@@ -746,8 +769,9 @@
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
-    </row>
-    <row r="6" spans="1:19" ht="13.2">
+      <c r="R5" s="14"/>
+    </row>
+    <row r="6" spans="1:19" ht="55.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -765,6 +789,9 @@
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
+      <c r="R6" s="15" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="7" spans="1:19" ht="13.2">
       <c r="A7" s="2"/>
@@ -784,8 +811,9 @@
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:19" ht="13.2">
+      <c r="R7" s="14"/>
+    </row>
+    <row r="8" spans="1:19" ht="69">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -803,6 +831,9 @@
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
+      <c r="R8" s="15" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="9" spans="1:19" ht="13.2">
       <c r="A9" s="2"/>
@@ -822,8 +853,9 @@
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
-    </row>
-    <row r="10" spans="1:19" ht="13.2">
+      <c r="R9" s="14"/>
+    </row>
+    <row r="10" spans="1:19" ht="69">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -841,6 +873,9 @@
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
+      <c r="R10" s="15" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="11" spans="1:19" ht="13.2">
       <c r="A11" s="2"/>
